--- a/examples/generate_preconfig/preconfig-advanced-vertical.xlsx
+++ b/examples/generate_preconfig/preconfig-advanced-vertical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/adam_wilkins_hpe_com/Documents/Documents/PycharmProjects/Pyedgeconnect_Dev/pyedgeconnect/examples/generate_preconfig/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{9C88CF1E-D92F-40F8-BAFE-118C6BEE4F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0141628-655F-4E5F-A745-2DB6D88023A6}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="13_ncr:1_{9C88CF1E-D92F-40F8-BAFE-118C6BEE4F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F7EB773-1E82-4A69-95E2-BC9C67D6F0DB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="930">
   <si>
     <t>Field</t>
   </si>
@@ -551,9 +551,6 @@
   </si>
   <si>
     <t>151.85.33.129</t>
-  </si>
-  <si>
-    <t>Unlimited</t>
   </si>
   <si>
     <t>EdgeHA1</t>
@@ -3034,10 +3031,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3331,7 +3324,7 @@
   <sheetFormatPr defaultColWidth="47.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.7265625" customWidth="1"/>
-    <col min="2" max="2" width="47.453125" style="3"/>
+    <col min="2" max="2" width="54.26953125" style="3" customWidth="1"/>
     <col min="7" max="7" width="47.453125" style="4"/>
   </cols>
   <sheetData>
@@ -3372,13 +3365,13 @@
         <v>153</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -3437,10 +3430,10 @@
         <v>165</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -3510,10 +3503,10 @@
         <v>165</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -3846,10 +3839,10 @@
         <v>169</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -4055,7 +4048,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>122</v>
@@ -4068,10 +4061,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -4081,10 +4074,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -4094,10 +4087,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -4107,10 +4100,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -4120,10 +4113,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
@@ -4133,10 +4126,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -4146,10 +4139,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -4159,10 +4152,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -4172,10 +4165,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -4185,10 +4178,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -4198,7 +4191,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="5"/>
@@ -4209,7 +4202,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="5"/>
@@ -4220,10 +4213,10 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -4233,10 +4226,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -4246,10 +4239,10 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -4259,10 +4252,10 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -4272,10 +4265,10 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -4285,10 +4278,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -4298,10 +4291,10 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -4311,7 +4304,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="5"/>
@@ -4322,10 +4315,10 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -4335,10 +4328,10 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -4348,10 +4341,10 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -4361,7 +4354,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="5"/>
@@ -4372,10 +4365,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -4385,10 +4378,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -4398,10 +4391,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -4411,10 +4404,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -4424,10 +4417,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -4437,10 +4430,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -4450,10 +4443,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -4463,7 +4456,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B79" s="6">
         <v>3600</v>
@@ -4476,7 +4469,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B80" s="6">
         <v>720</v>
@@ -4489,7 +4482,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B81" s="6">
         <v>150</v>
@@ -4502,10 +4495,10 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
@@ -4515,7 +4508,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="5"/>
@@ -4526,7 +4519,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="5"/>
@@ -4537,7 +4530,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="5"/>
@@ -4548,7 +4541,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="5"/>
@@ -4559,7 +4552,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B87" s="6">
         <v>152</v>
@@ -4572,10 +4565,10 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
@@ -4585,7 +4578,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B89" s="6">
         <v>153</v>
@@ -4598,10 +4591,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
@@ -4611,10 +4604,10 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -4624,10 +4617,10 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -4637,10 +4630,10 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -4650,10 +4643,10 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -4663,10 +4656,10 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -4676,10 +4669,10 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
@@ -4689,10 +4682,10 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -4702,10 +4695,10 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -4715,10 +4708,10 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -4728,10 +4721,10 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
@@ -4741,10 +4734,10 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -4754,10 +4747,10 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
@@ -4767,10 +4760,10 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -4780,10 +4773,10 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
@@ -4793,10 +4786,10 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -4806,10 +4799,10 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
@@ -4819,10 +4812,10 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
@@ -4832,10 +4825,10 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
@@ -4845,7 +4838,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B109" s="10"/>
       <c r="C109" s="10"/>
@@ -4856,7 +4849,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B110" s="10"/>
       <c r="C110" s="11"/>
@@ -4867,7 +4860,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B111" s="10"/>
       <c r="C111" s="11"/>
@@ -4878,7 +4871,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B112" s="10"/>
       <c r="C112" s="11"/>
@@ -4889,7 +4882,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B113" s="10"/>
       <c r="C113" s="11"/>
@@ -4900,7 +4893,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B114" s="10"/>
       <c r="C114" s="11"/>
@@ -4911,7 +4904,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B115" s="10"/>
       <c r="C115" s="11"/>
@@ -4922,7 +4915,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
@@ -4933,10 +4926,10 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -4946,10 +4939,10 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
@@ -4959,10 +4952,10 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
@@ -4972,10 +4965,10 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
@@ -4985,10 +4978,10 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
@@ -4998,10 +4991,10 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
@@ -5011,10 +5004,10 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
@@ -5024,10 +5017,10 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
@@ -5037,10 +5030,10 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
@@ -5050,10 +5043,10 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
@@ -5063,10 +5056,10 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
@@ -5076,7 +5069,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B128" s="6"/>
       <c r="C128" s="5"/>
@@ -5087,7 +5080,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B129" s="6"/>
       <c r="C129" s="5"/>
@@ -5098,10 +5091,10 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
@@ -5111,10 +5104,10 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
@@ -5124,10 +5117,10 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C132" s="5"/>
       <c r="D132" s="5"/>
@@ -5137,10 +5130,10 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
@@ -5150,10 +5143,10 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C134" s="5"/>
       <c r="D134" s="5"/>
@@ -5163,10 +5156,10 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
@@ -5176,10 +5169,10 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
@@ -5189,7 +5182,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B137" s="6"/>
       <c r="C137" s="5"/>
@@ -5200,10 +5193,10 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
@@ -5213,10 +5206,10 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
@@ -5226,10 +5219,10 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
@@ -5239,7 +5232,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="5"/>
@@ -5250,10 +5243,10 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
@@ -5263,10 +5256,10 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
@@ -5276,10 +5269,10 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
@@ -5289,10 +5282,10 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
@@ -5302,10 +5295,10 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C146" s="5"/>
       <c r="D146" s="5"/>
@@ -5315,10 +5308,10 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
@@ -5328,10 +5321,10 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C148" s="5"/>
       <c r="D148" s="5"/>
@@ -5341,7 +5334,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B149" s="6">
         <v>3600</v>
@@ -5354,7 +5347,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B150" s="6">
         <v>720</v>
@@ -5367,7 +5360,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B151" s="6">
         <v>150</v>
@@ -5380,10 +5373,10 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C152" s="5"/>
       <c r="D152" s="5"/>
@@ -5393,7 +5386,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B153" s="6"/>
       <c r="C153" s="5"/>
@@ -5404,7 +5397,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="5"/>
@@ -5415,7 +5408,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="5"/>
@@ -5426,7 +5419,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="5"/>
@@ -5437,7 +5430,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B157" s="6">
         <v>152</v>
@@ -5450,10 +5443,10 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C158" s="5"/>
       <c r="D158" s="5"/>
@@ -5463,7 +5456,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B159" s="6">
         <v>153</v>
@@ -5476,10 +5469,10 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
@@ -5489,10 +5482,10 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="5"/>
@@ -5502,10 +5495,10 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
@@ -5515,10 +5508,10 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
@@ -5528,10 +5521,10 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
@@ -5541,10 +5534,10 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
@@ -5554,10 +5547,10 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
@@ -5567,10 +5560,10 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
@@ -5580,10 +5573,10 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
@@ -5593,10 +5586,10 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
@@ -5606,10 +5599,10 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
@@ -5619,10 +5612,10 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
@@ -5632,10 +5625,10 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
@@ -5645,10 +5638,10 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
@@ -5658,10 +5651,10 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
@@ -5671,10 +5664,10 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
@@ -5684,10 +5677,10 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
@@ -5697,10 +5690,10 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
@@ -5710,10 +5703,10 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
@@ -5723,7 +5716,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B179" s="10"/>
       <c r="C179" s="5"/>
@@ -5734,7 +5727,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B180" s="10"/>
       <c r="C180" s="5"/>
@@ -5745,7 +5738,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B181" s="10"/>
       <c r="C181" s="5"/>
@@ -5756,7 +5749,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B182" s="10"/>
       <c r="C182" s="5"/>
@@ -5767,7 +5760,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B183" s="10"/>
       <c r="C183" s="5"/>
@@ -5778,7 +5771,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B184" s="10"/>
       <c r="C184" s="5"/>
@@ -5789,7 +5782,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B185" s="10"/>
       <c r="C185" s="5"/>
@@ -5800,7 +5793,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B186" s="10"/>
       <c r="C186" s="5"/>
@@ -5811,7 +5804,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B187" s="6"/>
       <c r="C187" s="5"/>
@@ -5822,7 +5815,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B188" s="6"/>
       <c r="C188" s="5"/>
@@ -5833,7 +5826,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B189" s="6"/>
       <c r="C189" s="5"/>
@@ -5844,7 +5837,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B190" s="6"/>
       <c r="C190" s="5"/>
@@ -5855,7 +5848,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B191" s="6"/>
       <c r="C191" s="5"/>
@@ -5866,7 +5859,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B192" s="6"/>
       <c r="C192" s="5"/>
@@ -5877,7 +5870,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B193" s="6"/>
       <c r="C193" s="5"/>
@@ -5888,7 +5881,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B194" s="6"/>
       <c r="C194" s="5"/>
@@ -5899,7 +5892,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B195" s="6"/>
       <c r="C195" s="5"/>
@@ -5910,7 +5903,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B196" s="6"/>
       <c r="C196" s="5"/>
@@ -5921,7 +5914,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B197" s="6"/>
       <c r="C197" s="5"/>
@@ -5932,7 +5925,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B198" s="6"/>
       <c r="C198" s="5"/>
@@ -5943,7 +5936,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B199" s="6"/>
       <c r="C199" s="5"/>
@@ -5954,7 +5947,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B200" s="6"/>
       <c r="C200" s="5"/>
@@ -5965,7 +5958,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B201" s="6"/>
       <c r="C201" s="5"/>
@@ -5976,7 +5969,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B202" s="6"/>
       <c r="C202" s="5"/>
@@ -5987,7 +5980,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B203" s="6"/>
       <c r="C203" s="5"/>
@@ -5998,7 +5991,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B204" s="6"/>
       <c r="C204" s="5"/>
@@ -6009,7 +6002,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B205" s="6"/>
       <c r="C205" s="5"/>
@@ -6020,7 +6013,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B206" s="6"/>
       <c r="C206" s="5"/>
@@ -6031,7 +6024,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B207" s="6"/>
       <c r="C207" s="5"/>
@@ -6042,7 +6035,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B208" s="6"/>
       <c r="C208" s="5"/>
@@ -6053,7 +6046,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B209" s="6"/>
       <c r="C209" s="5"/>
@@ -6064,7 +6057,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B210" s="6"/>
       <c r="C210" s="5"/>
@@ -6075,7 +6068,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B211" s="6"/>
       <c r="C211" s="5"/>
@@ -6086,7 +6079,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B212" s="6"/>
       <c r="C212" s="5"/>
@@ -6097,7 +6090,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B213" s="6"/>
       <c r="C213" s="5"/>
@@ -6108,7 +6101,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B214" s="6"/>
       <c r="C214" s="5"/>
@@ -6119,7 +6112,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B215" s="6"/>
       <c r="C215" s="5"/>
@@ -6130,7 +6123,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B216" s="6"/>
       <c r="C216" s="5"/>
@@ -6141,7 +6134,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B217" s="6"/>
       <c r="C217" s="5"/>
@@ -6152,7 +6145,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B218" s="6"/>
       <c r="C218" s="5"/>
@@ -6163,7 +6156,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B219" s="6"/>
       <c r="C219" s="5"/>
@@ -6174,7 +6167,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B220" s="6"/>
       <c r="C220" s="5"/>
@@ -6185,7 +6178,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B221" s="6"/>
       <c r="C221" s="5"/>
@@ -6196,7 +6189,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B222" s="6"/>
       <c r="C222" s="5"/>
@@ -6207,7 +6200,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B223" s="6"/>
       <c r="C223" s="5"/>
@@ -6218,7 +6211,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B224" s="6"/>
       <c r="C224" s="5"/>
@@ -6229,7 +6222,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B225" s="6"/>
       <c r="C225" s="5"/>
@@ -6240,7 +6233,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B226" s="6"/>
       <c r="C226" s="5"/>
@@ -6251,7 +6244,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B227" s="6"/>
       <c r="C227" s="5"/>
@@ -6262,7 +6255,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B228" s="6"/>
       <c r="C228" s="5"/>
@@ -6273,7 +6266,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B229" s="6"/>
       <c r="C229" s="5"/>
@@ -6284,7 +6277,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B230" s="6"/>
       <c r="C230" s="5"/>
@@ -6295,7 +6288,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B231" s="6"/>
       <c r="C231" s="5"/>
@@ -6306,7 +6299,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B232" s="6"/>
       <c r="C232" s="5"/>
@@ -6317,7 +6310,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B233" s="6"/>
       <c r="C233" s="5"/>
@@ -6328,7 +6321,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B234" s="6"/>
       <c r="C234" s="5"/>
@@ -6339,7 +6332,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B235" s="6"/>
       <c r="C235" s="5"/>
@@ -6350,7 +6343,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B236" s="6"/>
       <c r="C236" s="5"/>
@@ -6361,7 +6354,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B237" s="6"/>
       <c r="C237" s="5"/>
@@ -6372,7 +6365,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B238" s="6"/>
       <c r="C238" s="5"/>
@@ -6383,7 +6376,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B239" s="6"/>
       <c r="C239" s="5"/>
@@ -6394,7 +6387,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B240" s="6"/>
       <c r="C240" s="5"/>
@@ -6405,7 +6398,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B241" s="6"/>
       <c r="C241" s="5"/>
@@ -6416,7 +6409,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B242" s="6"/>
       <c r="C242" s="5"/>
@@ -6427,7 +6420,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B243" s="6"/>
       <c r="C243" s="5"/>
@@ -6438,7 +6431,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B244" s="6"/>
       <c r="C244" s="5"/>
@@ -6449,7 +6442,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B245" s="6"/>
       <c r="C245" s="5"/>
@@ -6460,7 +6453,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B246" s="6"/>
       <c r="C246" s="5"/>
@@ -6471,7 +6464,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B247" s="6"/>
       <c r="C247" s="5"/>
@@ -6482,7 +6475,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B248" s="6"/>
       <c r="C248" s="5"/>
@@ -6493,7 +6486,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B249" s="6"/>
       <c r="C249" s="5"/>
@@ -6504,7 +6497,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B250" s="6"/>
       <c r="C250" s="5"/>
@@ -6515,7 +6508,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B251" s="6"/>
       <c r="C251" s="5"/>
@@ -6526,7 +6519,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B252" s="6"/>
       <c r="C252" s="5"/>
@@ -6537,7 +6530,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B253" s="6"/>
       <c r="C253" s="5"/>
@@ -6548,7 +6541,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B254" s="6"/>
       <c r="C254" s="5"/>
@@ -6559,7 +6552,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B255" s="6"/>
       <c r="C255" s="5"/>
@@ -6570,7 +6563,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B256" s="6"/>
       <c r="C256" s="5"/>
@@ -6581,10 +6574,10 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
@@ -6594,10 +6587,10 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
@@ -6607,10 +6600,10 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
@@ -6620,10 +6613,10 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
@@ -6633,10 +6626,10 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
@@ -6646,10 +6639,10 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
@@ -6659,10 +6652,10 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
@@ -6672,10 +6665,10 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
@@ -6685,10 +6678,10 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
@@ -6698,10 +6691,10 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
@@ -6711,10 +6704,10 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
@@ -6724,7 +6717,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B268" s="6"/>
       <c r="C268" s="5"/>
@@ -6735,7 +6728,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B269" s="6"/>
       <c r="C269" s="5"/>
@@ -6746,10 +6739,10 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
@@ -6759,10 +6752,10 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
@@ -6772,10 +6765,10 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
@@ -6785,10 +6778,10 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
@@ -6798,10 +6791,10 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
@@ -6811,10 +6804,10 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
@@ -6824,10 +6817,10 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
@@ -6837,7 +6830,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B277" s="6"/>
       <c r="C277" s="5"/>
@@ -6848,10 +6841,10 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
@@ -6861,10 +6854,10 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
@@ -6874,10 +6867,10 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
@@ -6887,7 +6880,7 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B281" s="6"/>
       <c r="C281" s="5"/>
@@ -6898,10 +6891,10 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
@@ -6911,10 +6904,10 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
@@ -6924,10 +6917,10 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
@@ -6937,10 +6930,10 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
@@ -6950,10 +6943,10 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
@@ -6963,10 +6956,10 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
@@ -6976,10 +6969,10 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
@@ -6989,7 +6982,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B289" s="6">
         <v>3600</v>
@@ -7002,7 +6995,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B290" s="6">
         <v>720</v>
@@ -7015,7 +7008,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B291" s="6">
         <v>150</v>
@@ -7028,10 +7021,10 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
@@ -7041,7 +7034,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B293" s="6"/>
       <c r="C293" s="5"/>
@@ -7052,7 +7045,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B294" s="6"/>
       <c r="C294" s="5"/>
@@ -7063,7 +7056,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B295" s="6"/>
       <c r="C295" s="5"/>
@@ -7074,7 +7067,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B296" s="6"/>
       <c r="C296" s="5"/>
@@ -7085,7 +7078,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B297" s="6">
         <v>152</v>
@@ -7098,10 +7091,10 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C298" s="5"/>
       <c r="D298" s="5"/>
@@ -7111,7 +7104,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B299" s="6">
         <v>153</v>
@@ -7124,10 +7117,10 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
@@ -7137,10 +7130,10 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
@@ -7150,10 +7143,10 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C302" s="5"/>
       <c r="D302" s="5"/>
@@ -7163,10 +7156,10 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C303" s="5"/>
       <c r="D303" s="5"/>
@@ -7176,10 +7169,10 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C304" s="5"/>
       <c r="D304" s="5"/>
@@ -7189,10 +7182,10 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C305" s="5"/>
       <c r="D305" s="5"/>
@@ -7202,10 +7195,10 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C306" s="5"/>
       <c r="D306" s="5"/>
@@ -7215,10 +7208,10 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C307" s="5"/>
       <c r="D307" s="5"/>
@@ -7228,10 +7221,10 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C308" s="5"/>
       <c r="D308" s="5"/>
@@ -7241,10 +7234,10 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C309" s="5"/>
       <c r="D309" s="5"/>
@@ -7254,10 +7247,10 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C310" s="5"/>
       <c r="D310" s="5"/>
@@ -7267,10 +7260,10 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C311" s="5"/>
       <c r="D311" s="5"/>
@@ -7280,10 +7273,10 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
@@ -7293,10 +7286,10 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C313" s="5"/>
       <c r="D313" s="5"/>
@@ -7306,10 +7299,10 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C314" s="5"/>
       <c r="D314" s="5"/>
@@ -7319,10 +7312,10 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C315" s="5"/>
       <c r="D315" s="5"/>
@@ -7332,10 +7325,10 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C316" s="5"/>
       <c r="D316" s="5"/>
@@ -7345,10 +7338,10 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C317" s="5"/>
       <c r="D317" s="5"/>
@@ -7358,10 +7351,10 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
@@ -7371,7 +7364,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B319" s="6"/>
       <c r="C319" s="5"/>
@@ -7382,7 +7375,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B320" s="6"/>
       <c r="C320" s="5"/>
@@ -7393,7 +7386,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B321" s="6"/>
       <c r="C321" s="5"/>
@@ -7404,7 +7397,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B322" s="6"/>
       <c r="C322" s="5"/>
@@ -7415,7 +7408,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B323" s="6"/>
       <c r="C323" s="5"/>
@@ -7426,7 +7419,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B324" s="6"/>
       <c r="C324" s="5"/>
@@ -7437,7 +7430,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B325" s="6"/>
       <c r="C325" s="5"/>
@@ -7448,7 +7441,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B326" s="6"/>
       <c r="C326" s="5"/>
@@ -7459,7 +7452,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B327" s="6"/>
       <c r="C327" s="5"/>
@@ -7470,7 +7463,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B328" s="6"/>
       <c r="C328" s="5"/>
@@ -7481,7 +7474,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B329" s="6"/>
       <c r="C329" s="5"/>
@@ -7492,7 +7485,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B330" s="6"/>
       <c r="C330" s="5"/>
@@ -7503,7 +7496,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B331" s="6"/>
       <c r="C331" s="5"/>
@@ -7514,7 +7507,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B332" s="6"/>
       <c r="C332" s="5"/>
@@ -7525,7 +7518,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B333" s="6"/>
       <c r="C333" s="5"/>
@@ -7536,7 +7529,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B334" s="6"/>
       <c r="C334" s="5"/>
@@ -7547,7 +7540,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B335" s="6"/>
       <c r="C335" s="5"/>
@@ -7558,7 +7551,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B336" s="6"/>
       <c r="C336" s="5"/>
@@ -7569,7 +7562,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B337" s="6"/>
       <c r="C337" s="5"/>
@@ -7580,7 +7573,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B338" s="6"/>
       <c r="C338" s="5"/>
@@ -7591,7 +7584,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B339" s="6"/>
       <c r="C339" s="5"/>
@@ -7602,7 +7595,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B340" s="6"/>
       <c r="C340" s="5"/>
@@ -7613,7 +7606,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B341" s="6"/>
       <c r="C341" s="5"/>
@@ -7624,7 +7617,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B342" s="6"/>
       <c r="C342" s="5"/>
@@ -7635,7 +7628,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B343" s="6"/>
       <c r="C343" s="5"/>
@@ -7646,7 +7639,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B344" s="6"/>
       <c r="C344" s="5"/>
@@ -7657,7 +7650,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B345" s="6"/>
       <c r="C345" s="5"/>
@@ -7668,7 +7661,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B346" s="6"/>
       <c r="C346" s="5"/>
@@ -7679,7 +7672,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B347" s="6"/>
       <c r="C347" s="5"/>
@@ -7690,7 +7683,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B348" s="6"/>
       <c r="C348" s="5"/>
@@ -7701,7 +7694,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B349" s="6"/>
       <c r="C349" s="5"/>
@@ -7712,7 +7705,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B350" s="6"/>
       <c r="C350" s="5"/>
@@ -7723,7 +7716,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B351" s="6"/>
       <c r="C351" s="5"/>
@@ -7734,7 +7727,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B352" s="6"/>
       <c r="C352" s="5"/>
@@ -7745,7 +7738,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B353" s="6"/>
       <c r="C353" s="5"/>
@@ -7756,7 +7749,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B354" s="6"/>
       <c r="C354" s="5"/>
@@ -7767,7 +7760,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B355" s="6"/>
       <c r="C355" s="5"/>
@@ -7778,7 +7771,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B356" s="6"/>
       <c r="C356" s="5"/>
@@ -7789,7 +7782,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B357" s="6"/>
       <c r="C357" s="5"/>
@@ -7800,7 +7793,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B358" s="6"/>
       <c r="C358" s="5"/>
@@ -7811,7 +7804,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B359" s="6"/>
       <c r="C359" s="5"/>
@@ -7822,7 +7815,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B360" s="6"/>
       <c r="C360" s="5"/>
@@ -7833,7 +7826,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B361" s="6"/>
       <c r="C361" s="5"/>
@@ -7844,7 +7837,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B362" s="6"/>
       <c r="C362" s="5"/>
@@ -7855,7 +7848,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B363" s="6"/>
       <c r="C363" s="5"/>
@@ -7866,7 +7859,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B364" s="6"/>
       <c r="C364" s="5"/>
@@ -7877,7 +7870,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B365" s="6"/>
       <c r="C365" s="5"/>
@@ -7888,7 +7881,7 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B366" s="6"/>
       <c r="C366" s="5"/>
@@ -7899,7 +7892,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B367" s="6"/>
       <c r="C367" s="5"/>
@@ -7910,7 +7903,7 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B368" s="6"/>
       <c r="C368" s="5"/>
@@ -7921,7 +7914,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B369" s="6"/>
       <c r="C369" s="5"/>
@@ -7932,7 +7925,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B370" s="6"/>
       <c r="C370" s="5"/>
@@ -7943,7 +7936,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B371" s="6"/>
       <c r="C371" s="5"/>
@@ -7954,7 +7947,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B372" s="6"/>
       <c r="C372" s="5"/>
@@ -7965,7 +7958,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B373" s="6"/>
       <c r="C373" s="5"/>
@@ -7976,7 +7969,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B374" s="6"/>
       <c r="C374" s="5"/>
@@ -7987,7 +7980,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B375" s="6"/>
       <c r="C375" s="5"/>
@@ -7998,7 +7991,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B376" s="6"/>
       <c r="C376" s="5"/>
@@ -8009,7 +8002,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B377" s="6"/>
       <c r="C377" s="5"/>
@@ -8020,7 +8013,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B378" s="6"/>
       <c r="C378" s="5"/>
@@ -8031,7 +8024,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B379" s="6"/>
       <c r="C379" s="5"/>
@@ -8042,7 +8035,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B380" s="6"/>
       <c r="C380" s="5"/>
@@ -8053,7 +8046,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B381" s="6"/>
       <c r="C381" s="5"/>
@@ -8064,7 +8057,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B382" s="6"/>
       <c r="C382" s="5"/>
@@ -8075,7 +8068,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B383" s="6"/>
       <c r="C383" s="5"/>
@@ -8086,7 +8079,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B384" s="6"/>
       <c r="C384" s="5"/>
@@ -8097,7 +8090,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B385" s="6"/>
       <c r="C385" s="5"/>
@@ -8108,7 +8101,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B386" s="6"/>
       <c r="C386" s="5"/>
@@ -8119,7 +8112,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B387" s="6"/>
       <c r="C387" s="5"/>
@@ -8130,7 +8123,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B388" s="6"/>
       <c r="C388" s="5"/>
@@ -8141,7 +8134,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B389" s="6"/>
       <c r="C389" s="5"/>
@@ -8152,7 +8145,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="8" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B390" s="6"/>
       <c r="C390" s="5"/>
@@ -8163,7 +8156,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B391" s="6"/>
       <c r="C391" s="5"/>
@@ -8174,7 +8167,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B392" s="6"/>
       <c r="C392" s="5"/>
@@ -8185,7 +8178,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B393" s="6"/>
       <c r="C393" s="5"/>
@@ -8196,7 +8189,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B394" s="6"/>
       <c r="C394" s="5"/>
@@ -8207,7 +8200,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B395" s="6"/>
       <c r="C395" s="5"/>
@@ -8218,7 +8211,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B396" s="6"/>
       <c r="C396" s="5"/>
@@ -8229,7 +8222,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B397" s="6"/>
       <c r="C397" s="5"/>
@@ -8240,7 +8233,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B398" s="6"/>
       <c r="C398" s="5"/>
@@ -8251,7 +8244,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="8" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B399" s="6"/>
       <c r="C399" s="5"/>
@@ -8262,7 +8255,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B400" s="6"/>
       <c r="C400" s="5"/>
@@ -8273,7 +8266,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B401" s="6"/>
       <c r="C401" s="5"/>
@@ -8284,7 +8277,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="8" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B402" s="6"/>
       <c r="C402" s="5"/>
@@ -8295,7 +8288,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B403" s="6"/>
       <c r="C403" s="5"/>
@@ -8306,7 +8299,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B404" s="6"/>
       <c r="C404" s="5"/>
@@ -8317,7 +8310,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="8" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B405" s="6"/>
       <c r="C405" s="5"/>
@@ -8328,7 +8321,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B406" s="6"/>
       <c r="C406" s="5"/>
@@ -8339,7 +8332,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B407" s="6"/>
       <c r="C407" s="5"/>
@@ -8350,7 +8343,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="8" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B408" s="6"/>
       <c r="C408" s="5"/>
@@ -8361,7 +8354,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B409" s="6"/>
       <c r="C409" s="5"/>
@@ -8372,7 +8365,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B410" s="6"/>
       <c r="C410" s="5"/>
@@ -8383,7 +8376,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B411" s="6"/>
       <c r="C411" s="5"/>
@@ -8394,7 +8387,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B412" s="6"/>
       <c r="C412" s="5"/>
@@ -8405,7 +8398,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B413" s="6"/>
       <c r="C413" s="5"/>
@@ -8416,7 +8409,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B414" s="6"/>
       <c r="C414" s="5"/>
@@ -8427,7 +8420,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B415" s="6"/>
       <c r="C415" s="5"/>
@@ -8438,7 +8431,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B416" s="6"/>
       <c r="C416" s="5"/>
@@ -8449,7 +8442,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="8" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B417" s="6"/>
       <c r="C417" s="5"/>
@@ -8460,7 +8453,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B418" s="6"/>
       <c r="C418" s="5"/>
@@ -8471,7 +8464,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B419" s="6"/>
       <c r="C419" s="5"/>
@@ -8482,7 +8475,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B420" s="6"/>
       <c r="C420" s="5"/>
@@ -8493,7 +8486,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B421" s="6"/>
       <c r="C421" s="5"/>
@@ -8504,7 +8497,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="8" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B422" s="6"/>
       <c r="C422" s="5"/>
@@ -8515,7 +8508,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B423" s="6"/>
       <c r="C423" s="5"/>
@@ -8526,7 +8519,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B424" s="6"/>
       <c r="C424" s="5"/>
@@ -8537,7 +8530,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B425" s="6"/>
       <c r="C425" s="5"/>
@@ -8548,7 +8541,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="8" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B426" s="6"/>
       <c r="C426" s="5"/>
@@ -8559,7 +8552,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B427" s="6"/>
       <c r="C427" s="5"/>
@@ -8570,7 +8563,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B428" s="6"/>
       <c r="C428" s="5"/>
@@ -8581,7 +8574,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B429" s="6"/>
       <c r="C429" s="5"/>
@@ -8592,7 +8585,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="8" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B430" s="6"/>
       <c r="C430" s="5"/>
@@ -8603,7 +8596,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="8" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B431" s="6"/>
       <c r="C431" s="5"/>
@@ -8614,7 +8607,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="8" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B432" s="6"/>
       <c r="C432" s="5"/>
@@ -8625,7 +8618,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="8" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B433" s="6"/>
       <c r="C433" s="5"/>
@@ -8636,7 +8629,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B434" s="6"/>
       <c r="C434" s="5"/>
@@ -8647,7 +8640,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="8" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B435" s="6"/>
       <c r="C435" s="5"/>
@@ -8658,7 +8651,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B436" s="6"/>
       <c r="C436" s="5"/>
@@ -8669,7 +8662,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B437" s="6"/>
       <c r="C437" s="5"/>
@@ -8680,7 +8673,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B438" s="6"/>
       <c r="C438" s="5"/>
@@ -8691,7 +8684,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B439" s="6"/>
       <c r="C439" s="5"/>
@@ -8702,7 +8695,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B440" s="6"/>
       <c r="C440" s="5"/>
@@ -8713,7 +8706,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B441" s="6"/>
       <c r="C441" s="5"/>
@@ -8724,7 +8717,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="8" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B442" s="6"/>
       <c r="C442" s="5"/>
@@ -8735,7 +8728,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B443" s="6"/>
       <c r="C443" s="5"/>
@@ -8746,7 +8739,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B444" s="6"/>
       <c r="C444" s="5"/>
@@ -8757,7 +8750,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B445" s="6"/>
       <c r="C445" s="5"/>
@@ -8768,7 +8761,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B446" s="6"/>
       <c r="C446" s="5"/>
@@ -8779,7 +8772,7 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B447" s="6"/>
       <c r="C447" s="5"/>
@@ -8790,7 +8783,7 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B448" s="6"/>
       <c r="C448" s="5"/>
@@ -8801,7 +8794,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B449" s="6"/>
       <c r="C449" s="5"/>
@@ -8812,7 +8805,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B450" s="6"/>
       <c r="C450" s="5"/>
@@ -8823,7 +8816,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B451" s="6"/>
       <c r="C451" s="5"/>
@@ -8834,7 +8827,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="8" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B452" s="6"/>
       <c r="C452" s="5"/>
@@ -8845,7 +8838,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B453" s="6"/>
       <c r="C453" s="5"/>
@@ -8856,7 +8849,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B454" s="6"/>
       <c r="C454" s="5"/>
@@ -8867,7 +8860,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B455" s="6"/>
       <c r="C455" s="5"/>
@@ -8878,7 +8871,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B456" s="6"/>
       <c r="C456" s="5"/>
@@ -8889,7 +8882,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B457" s="6"/>
       <c r="C457" s="5"/>
@@ -8900,7 +8893,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B458" s="6"/>
       <c r="C458" s="5"/>
@@ -8911,7 +8904,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B459" s="6"/>
       <c r="C459" s="5"/>
@@ -8922,7 +8915,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B460" s="6"/>
       <c r="C460" s="5"/>
@@ -8933,7 +8926,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B461" s="6"/>
       <c r="C461" s="5"/>
@@ -8944,7 +8937,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B462" s="6"/>
       <c r="C462" s="5"/>
@@ -8955,7 +8948,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B463" s="6"/>
       <c r="C463" s="5"/>
@@ -8966,7 +8959,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B464" s="6"/>
       <c r="C464" s="5"/>
@@ -8977,7 +8970,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B465" s="6"/>
       <c r="C465" s="5"/>
@@ -8988,7 +8981,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B466" s="6"/>
       <c r="C466" s="5"/>
@@ -8999,7 +8992,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B467" s="6"/>
       <c r="C467" s="5"/>
@@ -9010,7 +9003,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B468" s="6"/>
       <c r="C468" s="5"/>
@@ -9021,7 +9014,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B469" s="6"/>
       <c r="C469" s="5"/>
@@ -9032,7 +9025,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="8" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B470" s="6"/>
       <c r="C470" s="5"/>
@@ -9043,7 +9036,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B471" s="6"/>
       <c r="C471" s="5"/>
@@ -9054,7 +9047,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B472" s="6"/>
       <c r="C472" s="5"/>
@@ -9065,7 +9058,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B473" s="6"/>
       <c r="C473" s="5"/>
@@ -9076,7 +9069,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B474" s="6"/>
       <c r="C474" s="5"/>
@@ -9087,7 +9080,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B475" s="6"/>
       <c r="C475" s="5"/>
@@ -9098,7 +9091,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B476" s="6"/>
       <c r="C476" s="5"/>
@@ -9109,7 +9102,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B477" s="6"/>
       <c r="C477" s="5"/>
@@ -9120,7 +9113,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B478" s="6"/>
       <c r="C478" s="5"/>
@@ -9131,7 +9124,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B479" s="6"/>
       <c r="C479" s="5"/>
@@ -9142,7 +9135,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A480" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B480" s="6"/>
       <c r="C480" s="5"/>
@@ -9153,7 +9146,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A481" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B481" s="6"/>
       <c r="C481" s="5"/>
@@ -9164,7 +9157,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A482" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B482" s="6"/>
       <c r="C482" s="5"/>
@@ -9175,7 +9168,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A483" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B483" s="6"/>
       <c r="C483" s="5"/>
@@ -9186,7 +9179,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A484" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B484" s="6"/>
       <c r="C484" s="5"/>
@@ -9197,7 +9190,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A485" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B485" s="6"/>
       <c r="C485" s="5"/>
@@ -9208,7 +9201,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A486" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B486" s="6"/>
       <c r="C486" s="5"/>
@@ -9219,7 +9212,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A487" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B487" s="6"/>
       <c r="C487" s="5"/>
@@ -9230,7 +9223,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A488" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B488" s="6"/>
       <c r="C488" s="5"/>
@@ -9241,7 +9234,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A489" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B489" s="6"/>
       <c r="C489" s="5"/>
@@ -9252,7 +9245,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A490" s="8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B490" s="6"/>
       <c r="C490" s="5"/>
@@ -9263,7 +9256,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A491" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B491" s="6"/>
       <c r="C491" s="5"/>
@@ -9274,7 +9267,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A492" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B492" s="6"/>
       <c r="C492" s="5"/>
@@ -9285,7 +9278,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A493" s="8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B493" s="6"/>
       <c r="C493" s="5"/>
@@ -9296,7 +9289,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A494" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B494" s="6"/>
       <c r="C494" s="5"/>
@@ -9307,7 +9300,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A495" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B495" s="6"/>
       <c r="C495" s="5"/>
@@ -9318,7 +9311,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A496" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B496" s="6"/>
       <c r="C496" s="5"/>
@@ -9329,7 +9322,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A497" s="8" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B497" s="6"/>
       <c r="C497" s="5"/>
@@ -9340,7 +9333,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A498" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B498" s="6"/>
       <c r="C498" s="5"/>
@@ -9351,7 +9344,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A499" s="8" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B499" s="6"/>
       <c r="C499" s="5"/>
@@ -9362,7 +9355,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A500" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B500" s="6"/>
       <c r="C500" s="5"/>
@@ -9373,7 +9366,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A501" s="8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B501" s="6"/>
       <c r="C501" s="5"/>
@@ -9384,7 +9377,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A502" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B502" s="6"/>
       <c r="C502" s="5"/>
@@ -9395,7 +9388,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A503" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B503" s="6"/>
       <c r="C503" s="5"/>
@@ -9406,7 +9399,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A504" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B504" s="6"/>
       <c r="C504" s="5"/>
@@ -9417,7 +9410,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A505" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B505" s="6"/>
       <c r="C505" s="5"/>
@@ -9428,7 +9421,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A506" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B506" s="6"/>
       <c r="C506" s="5"/>
@@ -9439,7 +9432,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A507" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B507" s="6"/>
       <c r="C507" s="5"/>
@@ -9450,7 +9443,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A508" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B508" s="6"/>
       <c r="C508" s="5"/>
@@ -9461,7 +9454,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A509" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B509" s="6"/>
       <c r="C509" s="5"/>
@@ -9472,7 +9465,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A510" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B510" s="6"/>
       <c r="C510" s="5"/>
@@ -9483,7 +9476,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A511" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B511" s="6"/>
       <c r="C511" s="5"/>
@@ -9494,7 +9487,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A512" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B512" s="6"/>
       <c r="C512" s="5"/>
@@ -9505,7 +9498,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A513" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B513" s="6"/>
       <c r="C513" s="5"/>
@@ -9516,7 +9509,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A514" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B514" s="6"/>
       <c r="C514" s="5"/>
@@ -9527,7 +9520,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A515" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B515" s="6"/>
       <c r="C515" s="5"/>
@@ -9538,7 +9531,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A516" s="8" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B516" s="6"/>
       <c r="C516" s="5"/>
@@ -9549,7 +9542,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A517" s="8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B517" s="6"/>
       <c r="C517" s="5"/>
@@ -9560,7 +9553,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A518" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B518" s="6"/>
       <c r="C518" s="5"/>
@@ -9571,7 +9564,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A519" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B519" s="6"/>
       <c r="C519" s="5"/>
@@ -9582,7 +9575,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A520" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B520" s="6"/>
       <c r="C520" s="5"/>
@@ -9593,7 +9586,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A521" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B521" s="6"/>
       <c r="C521" s="5"/>
@@ -9604,7 +9597,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A522" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B522" s="6"/>
       <c r="C522" s="5"/>
@@ -9615,7 +9608,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A523" s="8" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B523" s="6"/>
       <c r="C523" s="5"/>
@@ -9626,7 +9619,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A524" s="8" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B524" s="6"/>
       <c r="C524" s="5"/>
@@ -9637,7 +9630,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A525" s="8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B525" s="6"/>
       <c r="C525" s="5"/>
@@ -9648,7 +9641,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A526" s="8" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B526" s="6"/>
       <c r="C526" s="5"/>
@@ -9659,7 +9652,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A527" s="8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B527" s="6"/>
       <c r="C527" s="5"/>
@@ -9670,7 +9663,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A528" s="8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B528" s="6"/>
       <c r="C528" s="5"/>
@@ -9681,7 +9674,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A529" s="8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B529" s="6"/>
       <c r="C529" s="5"/>
@@ -9692,7 +9685,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A530" s="8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B530" s="6"/>
       <c r="C530" s="5"/>
@@ -9703,7 +9696,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A531" s="8" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B531" s="6"/>
       <c r="C531" s="5"/>
@@ -9714,7 +9707,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A532" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B532" s="6"/>
       <c r="C532" s="5"/>
@@ -9725,7 +9718,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A533" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B533" s="6"/>
       <c r="C533" s="5"/>
@@ -9736,7 +9729,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A534" s="8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B534" s="6"/>
       <c r="C534" s="5"/>
@@ -9747,7 +9740,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A535" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B535" s="6"/>
       <c r="C535" s="5"/>
@@ -9758,7 +9751,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A536" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B536" s="6"/>
       <c r="C536" s="5"/>
@@ -9769,7 +9762,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A537" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B537" s="6"/>
       <c r="C537" s="5"/>
@@ -9780,7 +9773,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A538" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B538" s="6"/>
       <c r="C538" s="5"/>
@@ -9791,7 +9784,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A539" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B539" s="6"/>
       <c r="C539" s="5"/>
@@ -9802,7 +9795,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A540" s="8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B540" s="6"/>
       <c r="C540" s="5"/>
@@ -9813,7 +9806,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A541" s="8" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B541" s="6"/>
       <c r="C541" s="5"/>
@@ -9824,7 +9817,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A542" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B542" s="6"/>
       <c r="C542" s="5"/>
@@ -9835,7 +9828,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A543" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B543" s="6"/>
       <c r="C543" s="5"/>
@@ -9846,7 +9839,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A544" s="8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B544" s="6"/>
       <c r="C544" s="5"/>
@@ -9857,7 +9850,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A545" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B545" s="6"/>
       <c r="C545" s="5"/>
@@ -9868,7 +9861,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A546" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B546" s="6"/>
       <c r="C546" s="5"/>
@@ -9879,7 +9872,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A547" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B547" s="6"/>
       <c r="C547" s="5"/>
@@ -9890,7 +9883,7 @@
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A548" s="8" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B548" s="6"/>
       <c r="C548" s="5"/>
@@ -9901,7 +9894,7 @@
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A549" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B549" s="6"/>
       <c r="C549" s="5"/>
@@ -9912,7 +9905,7 @@
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A550" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B550" s="6"/>
       <c r="C550" s="5"/>
@@ -9923,7 +9916,7 @@
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A551" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B551" s="6"/>
       <c r="C551" s="5"/>
@@ -9934,7 +9927,7 @@
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A552" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B552" s="6"/>
       <c r="C552" s="5"/>
@@ -9945,7 +9938,7 @@
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A553" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B553" s="6"/>
       <c r="C553" s="5"/>
@@ -9956,7 +9949,7 @@
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A554" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B554" s="6"/>
       <c r="C554" s="5"/>
@@ -9967,7 +9960,7 @@
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A555" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B555" s="6"/>
       <c r="C555" s="5"/>
@@ -9978,7 +9971,7 @@
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A556" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B556" s="6"/>
       <c r="C556" s="5"/>
@@ -9989,7 +9982,7 @@
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A557" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B557" s="6"/>
       <c r="C557" s="5"/>
@@ -10000,7 +9993,7 @@
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A558" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B558" s="6"/>
       <c r="C558" s="5"/>
@@ -10011,7 +10004,7 @@
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A559" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B559" s="6"/>
       <c r="C559" s="5"/>
@@ -10022,7 +10015,7 @@
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A560" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B560" s="6"/>
       <c r="C560" s="5"/>
@@ -10033,7 +10026,7 @@
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A561" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B561" s="6"/>
       <c r="C561" s="5"/>
@@ -10044,7 +10037,7 @@
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A562" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B562" s="6"/>
       <c r="C562" s="5"/>
@@ -10055,7 +10048,7 @@
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A563" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B563" s="6"/>
       <c r="C563" s="5"/>
@@ -10066,7 +10059,7 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A564" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B564" s="6"/>
       <c r="C564" s="5"/>
@@ -10077,7 +10070,7 @@
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A565" s="8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B565" s="6"/>
       <c r="C565" s="5"/>
@@ -10088,7 +10081,7 @@
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A566" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B566" s="6"/>
       <c r="C566" s="5"/>
@@ -10099,7 +10092,7 @@
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A567" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B567" s="6"/>
       <c r="C567" s="5"/>
@@ -10110,7 +10103,7 @@
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A568" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B568" s="6"/>
       <c r="C568" s="5"/>
@@ -10121,7 +10114,7 @@
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A569" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B569" s="6"/>
       <c r="C569" s="5"/>
@@ -10132,7 +10125,7 @@
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A570" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B570" s="6"/>
       <c r="C570" s="5"/>
@@ -10143,7 +10136,7 @@
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A571" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B571" s="6"/>
       <c r="C571" s="5"/>
@@ -10154,7 +10147,7 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A572" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B572" s="6"/>
       <c r="C572" s="5"/>
@@ -10165,7 +10158,7 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A573" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B573" s="6"/>
       <c r="C573" s="5"/>
@@ -10176,7 +10169,7 @@
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A574" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B574" s="6"/>
       <c r="C574" s="5"/>
@@ -10187,7 +10180,7 @@
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A575" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B575" s="6"/>
       <c r="C575" s="5"/>
@@ -10198,7 +10191,7 @@
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A576" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B576" s="6"/>
       <c r="C576" s="5"/>
@@ -10209,7 +10202,7 @@
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A577" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B577" s="6"/>
       <c r="C577" s="5"/>
@@ -10220,7 +10213,7 @@
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A578" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B578" s="6"/>
       <c r="C578" s="5"/>
@@ -10231,7 +10224,7 @@
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A579" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B579" s="6"/>
       <c r="C579" s="5"/>
@@ -10242,7 +10235,7 @@
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A580" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B580" s="6"/>
       <c r="C580" s="5"/>
@@ -10253,7 +10246,7 @@
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A581" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B581" s="6"/>
       <c r="C581" s="5"/>
@@ -10264,7 +10257,7 @@
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A582" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B582" s="6"/>
       <c r="C582" s="5"/>
@@ -10275,7 +10268,7 @@
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A583" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B583" s="6"/>
       <c r="C583" s="5"/>
@@ -10286,7 +10279,7 @@
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A584" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B584" s="6"/>
       <c r="C584" s="5"/>
@@ -10297,7 +10290,7 @@
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A585" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B585" s="6"/>
       <c r="C585" s="5"/>
@@ -10308,7 +10301,7 @@
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A586" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B586" s="6"/>
       <c r="C586" s="5"/>
@@ -10319,7 +10312,7 @@
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A587" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B587" s="6"/>
       <c r="C587" s="5"/>
@@ -10330,7 +10323,7 @@
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A588" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B588" s="6"/>
       <c r="C588" s="5"/>
@@ -10341,7 +10334,7 @@
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A589" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B589" s="6"/>
       <c r="C589" s="5"/>
@@ -10352,7 +10345,7 @@
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A590" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B590" s="6"/>
       <c r="C590" s="5"/>
@@ -10363,7 +10356,7 @@
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A591" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B591" s="6"/>
       <c r="C591" s="5"/>
@@ -10374,7 +10367,7 @@
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A592" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B592" s="6"/>
       <c r="C592" s="5"/>
@@ -10385,7 +10378,7 @@
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A593" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B593" s="6"/>
       <c r="C593" s="5"/>
@@ -10396,7 +10389,7 @@
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A594" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B594" s="6"/>
       <c r="C594" s="5"/>
@@ -10407,7 +10400,7 @@
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A595" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B595" s="6"/>
       <c r="C595" s="5"/>
@@ -10418,7 +10411,7 @@
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A596" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B596" s="6"/>
       <c r="C596" s="5"/>
@@ -10429,7 +10422,7 @@
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A597" s="8" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B597" s="6"/>
       <c r="C597" s="5"/>
@@ -10440,7 +10433,7 @@
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A598" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B598" s="6"/>
       <c r="C598" s="5"/>
@@ -10451,7 +10444,7 @@
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A599" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B599" s="6"/>
       <c r="C599" s="5"/>
@@ -10462,7 +10455,7 @@
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A600" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B600" s="6"/>
       <c r="C600" s="5"/>
@@ -10473,7 +10466,7 @@
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A601" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B601" s="6"/>
       <c r="C601" s="5"/>
@@ -10484,7 +10477,7 @@
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A602" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B602" s="6"/>
       <c r="C602" s="5"/>
@@ -10495,7 +10488,7 @@
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A603" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B603" s="6"/>
       <c r="C603" s="5"/>
@@ -10506,7 +10499,7 @@
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A604" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B604" s="6"/>
       <c r="C604" s="5"/>
@@ -10517,7 +10510,7 @@
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A605" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B605" s="6"/>
       <c r="C605" s="5"/>
@@ -10528,7 +10521,7 @@
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A606" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B606" s="6"/>
       <c r="C606" s="5"/>
@@ -10539,7 +10532,7 @@
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A607" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B607" s="6"/>
       <c r="C607" s="5"/>
@@ -10550,7 +10543,7 @@
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A608" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B608" s="6"/>
       <c r="C608" s="5"/>
@@ -10561,7 +10554,7 @@
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A609" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B609" s="6"/>
       <c r="C609" s="5"/>
@@ -10572,7 +10565,7 @@
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A610" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B610" s="6"/>
       <c r="C610" s="5"/>
@@ -10583,7 +10576,7 @@
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A611" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B611" s="6"/>
       <c r="C611" s="5"/>
@@ -10594,7 +10587,7 @@
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A612" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B612" s="6"/>
       <c r="C612" s="5"/>
@@ -10605,7 +10598,7 @@
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A613" s="8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B613" s="6"/>
       <c r="C613" s="5"/>
@@ -10616,7 +10609,7 @@
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A614" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B614" s="6"/>
       <c r="C614" s="5"/>
@@ -10627,7 +10620,7 @@
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A615" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B615" s="6"/>
       <c r="C615" s="5"/>
@@ -10638,7 +10631,7 @@
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A616" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B616" s="6"/>
       <c r="C616" s="5"/>
@@ -10649,7 +10642,7 @@
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A617" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B617" s="6"/>
       <c r="C617" s="5"/>
@@ -10660,7 +10653,7 @@
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A618" s="8" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B618" s="6"/>
       <c r="C618" s="5"/>
@@ -10671,7 +10664,7 @@
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A619" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B619" s="6"/>
       <c r="C619" s="5"/>
@@ -10682,7 +10675,7 @@
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A620" s="8" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B620" s="6"/>
       <c r="C620" s="5"/>
@@ -10693,7 +10686,7 @@
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A621" s="8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B621" s="6"/>
       <c r="C621" s="5"/>
@@ -10704,7 +10697,7 @@
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A622" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B622" s="6"/>
       <c r="C622" s="5"/>
@@ -10715,7 +10708,7 @@
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A623" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B623" s="6"/>
       <c r="C623" s="5"/>
@@ -10726,7 +10719,7 @@
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A624" s="8" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B624" s="6"/>
       <c r="C624" s="5"/>
@@ -10737,7 +10730,7 @@
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A625" s="8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B625" s="6"/>
       <c r="C625" s="5"/>
@@ -10748,7 +10741,7 @@
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A626" s="8" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B626" s="6"/>
       <c r="C626" s="5"/>
@@ -10759,7 +10752,7 @@
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A627" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B627" s="6"/>
       <c r="C627" s="5"/>
@@ -10770,7 +10763,7 @@
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A628" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B628" s="6"/>
       <c r="C628" s="5"/>
@@ -10781,7 +10774,7 @@
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A629" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B629" s="6"/>
       <c r="C629" s="5"/>
@@ -10792,7 +10785,7 @@
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A630" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B630" s="6"/>
       <c r="C630" s="5"/>
@@ -10803,7 +10796,7 @@
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A631" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B631" s="6"/>
       <c r="C631" s="5"/>
@@ -10814,7 +10807,7 @@
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A632" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B632" s="6"/>
       <c r="C632" s="5"/>
@@ -10825,7 +10818,7 @@
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A633" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B633" s="6"/>
       <c r="C633" s="5"/>
@@ -10836,7 +10829,7 @@
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A634" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B634" s="6"/>
       <c r="C634" s="5"/>
@@ -10847,7 +10840,7 @@
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A635" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B635" s="6"/>
       <c r="C635" s="5"/>
@@ -10858,7 +10851,7 @@
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A636" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B636" s="6"/>
       <c r="C636" s="5"/>
@@ -10869,7 +10862,7 @@
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A637" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B637" s="6"/>
       <c r="C637" s="5"/>
@@ -10880,7 +10873,7 @@
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A638" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B638" s="6"/>
       <c r="C638" s="5"/>
@@ -10891,7 +10884,7 @@
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A639" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B639" s="6"/>
       <c r="C639" s="5"/>
@@ -10902,7 +10895,7 @@
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A640" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B640" s="6"/>
       <c r="C640" s="5"/>
@@ -10913,7 +10906,7 @@
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A641" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B641" s="6"/>
       <c r="C641" s="5"/>
@@ -10924,7 +10917,7 @@
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A642" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B642" s="6"/>
       <c r="C642" s="5"/>
@@ -10935,7 +10928,7 @@
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A643" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B643" s="6"/>
       <c r="C643" s="5"/>
@@ -10946,7 +10939,7 @@
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A644" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B644" s="6"/>
       <c r="C644" s="5"/>
@@ -10957,7 +10950,7 @@
     </row>
     <row r="645" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A645" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B645" s="6"/>
       <c r="C645" s="5"/>
@@ -10968,7 +10961,7 @@
     </row>
     <row r="646" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A646" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B646" s="6"/>
       <c r="C646" s="5"/>
@@ -10979,7 +10972,7 @@
     </row>
     <row r="647" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A647" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B647" s="6"/>
       <c r="C647" s="5"/>
@@ -10990,7 +10983,7 @@
     </row>
     <row r="648" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A648" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B648" s="6"/>
       <c r="C648" s="5"/>
@@ -11001,7 +10994,7 @@
     </row>
     <row r="649" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A649" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B649" s="6"/>
       <c r="C649" s="5"/>
@@ -11012,7 +11005,7 @@
     </row>
     <row r="650" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A650" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B650" s="6"/>
       <c r="C650" s="5"/>
@@ -11023,7 +11016,7 @@
     </row>
     <row r="651" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A651" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B651" s="6"/>
       <c r="C651" s="5"/>
@@ -11034,7 +11027,7 @@
     </row>
     <row r="652" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A652" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B652" s="6"/>
       <c r="C652" s="5"/>
@@ -11045,7 +11038,7 @@
     </row>
     <row r="653" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A653" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B653" s="6"/>
       <c r="C653" s="5"/>
@@ -11056,7 +11049,7 @@
     </row>
     <row r="654" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A654" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B654" s="6"/>
       <c r="C654" s="5"/>
@@ -11067,7 +11060,7 @@
     </row>
     <row r="655" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A655" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B655" s="6"/>
       <c r="C655" s="5"/>
@@ -11078,7 +11071,7 @@
     </row>
     <row r="656" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A656" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B656" s="6"/>
       <c r="C656" s="5"/>
@@ -11089,7 +11082,7 @@
     </row>
     <row r="657" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A657" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B657" s="6"/>
       <c r="C657" s="5"/>
@@ -11100,7 +11093,7 @@
     </row>
     <row r="658" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A658" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B658" s="6"/>
       <c r="C658" s="5"/>
@@ -11111,7 +11104,7 @@
     </row>
     <row r="659" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A659" s="8" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B659" s="6"/>
       <c r="C659" s="5"/>
@@ -11122,7 +11115,7 @@
     </row>
     <row r="660" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A660" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B660" s="6"/>
       <c r="C660" s="5"/>
@@ -11133,7 +11126,7 @@
     </row>
     <row r="661" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A661" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B661" s="6"/>
       <c r="C661" s="5"/>
@@ -11144,7 +11137,7 @@
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A662" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B662" s="6"/>
       <c r="C662" s="5"/>
@@ -11155,7 +11148,7 @@
     </row>
     <row r="663" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A663" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B663" s="6"/>
       <c r="C663" s="5"/>
@@ -11166,7 +11159,7 @@
     </row>
     <row r="664" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A664" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B664" s="6"/>
       <c r="C664" s="5"/>
@@ -11177,7 +11170,7 @@
     </row>
     <row r="665" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A665" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B665" s="6"/>
       <c r="C665" s="5"/>
@@ -11188,7 +11181,7 @@
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A666" s="8" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B666" s="6"/>
       <c r="C666" s="5"/>
@@ -11199,7 +11192,7 @@
     </row>
     <row r="667" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A667" s="8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B667" s="6"/>
       <c r="C667" s="5"/>
@@ -11210,7 +11203,7 @@
     </row>
     <row r="668" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A668" s="8" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B668" s="6"/>
       <c r="C668" s="5"/>
@@ -11221,7 +11214,7 @@
     </row>
     <row r="669" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A669" s="8" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B669" s="6"/>
       <c r="C669" s="5"/>
@@ -11232,7 +11225,7 @@
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A670" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B670" s="6"/>
       <c r="C670" s="5"/>
@@ -11243,7 +11236,7 @@
     </row>
     <row r="671" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A671" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B671" s="6"/>
       <c r="C671" s="5"/>
@@ -11254,7 +11247,7 @@
     </row>
     <row r="672" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A672" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B672" s="6"/>
       <c r="C672" s="5"/>
@@ -11265,7 +11258,7 @@
     </row>
     <row r="673" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A673" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B673" s="6"/>
       <c r="C673" s="5"/>
@@ -11276,7 +11269,7 @@
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A674" s="8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B674" s="6"/>
       <c r="C674" s="5"/>
@@ -11287,7 +11280,7 @@
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A675" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B675" s="6"/>
       <c r="C675" s="5"/>
@@ -11298,7 +11291,7 @@
     </row>
     <row r="676" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A676" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B676" s="6"/>
       <c r="C676" s="5"/>
@@ -11309,7 +11302,7 @@
     </row>
     <row r="677" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A677" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B677" s="6"/>
       <c r="C677" s="5"/>
@@ -11320,7 +11313,7 @@
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A678" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B678" s="6"/>
       <c r="C678" s="5"/>
@@ -11331,7 +11324,7 @@
     </row>
     <row r="679" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A679" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B679" s="6"/>
       <c r="C679" s="5"/>
@@ -11342,7 +11335,7 @@
     </row>
     <row r="680" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A680" s="8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B680" s="6"/>
       <c r="C680" s="5"/>
@@ -11353,7 +11346,7 @@
     </row>
     <row r="681" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A681" s="8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B681" s="6"/>
       <c r="C681" s="5"/>
@@ -11364,7 +11357,7 @@
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A682" s="8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B682" s="6"/>
       <c r="C682" s="5"/>
@@ -11375,7 +11368,7 @@
     </row>
     <row r="683" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A683" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B683" s="6"/>
       <c r="C683" s="5"/>
@@ -11386,7 +11379,7 @@
     </row>
     <row r="684" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A684" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B684" s="6"/>
       <c r="C684" s="5"/>
@@ -11397,7 +11390,7 @@
     </row>
     <row r="685" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A685" s="8" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B685" s="6"/>
       <c r="C685" s="5"/>
@@ -11408,7 +11401,7 @@
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A686" s="8" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B686" s="6"/>
       <c r="C686" s="5"/>
@@ -11419,7 +11412,7 @@
     </row>
     <row r="687" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A687" s="8" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B687" s="6"/>
       <c r="C687" s="5"/>
@@ -11430,7 +11423,7 @@
     </row>
     <row r="688" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A688" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B688" s="6"/>
       <c r="C688" s="5"/>
@@ -11441,7 +11434,7 @@
     </row>
     <row r="689" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A689" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B689" s="6"/>
       <c r="C689" s="5"/>
@@ -11452,7 +11445,7 @@
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A690" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B690" s="6"/>
       <c r="C690" s="5"/>
@@ -11463,7 +11456,7 @@
     </row>
     <row r="691" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A691" s="8" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B691" s="6"/>
       <c r="C691" s="5"/>
@@ -11474,7 +11467,7 @@
     </row>
     <row r="692" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A692" s="8" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B692" s="6"/>
       <c r="C692" s="5"/>
@@ -11485,7 +11478,7 @@
     </row>
     <row r="693" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A693" s="8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B693" s="6"/>
       <c r="C693" s="5"/>
@@ -11496,7 +11489,7 @@
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A694" s="8" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B694" s="6"/>
       <c r="C694" s="5"/>
@@ -11507,7 +11500,7 @@
     </row>
     <row r="695" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A695" s="8" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B695" s="6"/>
       <c r="C695" s="5"/>
@@ -11518,7 +11511,7 @@
     </row>
     <row r="696" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A696" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B696" s="6"/>
       <c r="C696" s="5"/>
@@ -11529,7 +11522,7 @@
     </row>
     <row r="697" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A697" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B697" s="6"/>
       <c r="C697" s="5"/>
@@ -11540,7 +11533,7 @@
     </row>
     <row r="698" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A698" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B698" s="6"/>
       <c r="C698" s="5"/>
@@ -11551,7 +11544,7 @@
     </row>
     <row r="699" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A699" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B699" s="6"/>
       <c r="C699" s="5"/>
@@ -11562,7 +11555,7 @@
     </row>
     <row r="700" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A700" s="8" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B700" s="6"/>
       <c r="C700" s="5"/>
@@ -11573,7 +11566,7 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A701" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B701" s="6"/>
       <c r="C701" s="5"/>
@@ -11584,7 +11577,7 @@
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A702" s="8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B702" s="6"/>
       <c r="C702" s="5"/>
@@ -11595,7 +11588,7 @@
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A703" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B703" s="6"/>
       <c r="C703" s="5"/>
@@ -11606,7 +11599,7 @@
     </row>
     <row r="704" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A704" s="8" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B704" s="6"/>
       <c r="C704" s="5"/>
@@ -11617,7 +11610,7 @@
     </row>
     <row r="705" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A705" s="8" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B705" s="6"/>
       <c r="C705" s="5"/>
@@ -11628,7 +11621,7 @@
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A706" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B706" s="6"/>
       <c r="C706" s="5"/>
@@ -11639,7 +11632,7 @@
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A707" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B707" s="6"/>
       <c r="C707" s="5"/>
@@ -11650,7 +11643,7 @@
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A708" s="8" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B708" s="6"/>
       <c r="C708" s="5"/>
@@ -11661,7 +11654,7 @@
     </row>
     <row r="709" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A709" s="8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B709" s="6"/>
       <c r="C709" s="5"/>
@@ -11672,7 +11665,7 @@
     </row>
     <row r="710" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A710" s="8" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B710" s="6"/>
       <c r="C710" s="5"/>
@@ -11683,7 +11676,7 @@
     </row>
     <row r="711" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A711" s="8" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B711" s="6"/>
       <c r="C711" s="5"/>
@@ -11694,7 +11687,7 @@
     </row>
     <row r="712" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A712" s="8" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B712" s="6"/>
       <c r="C712" s="5"/>
@@ -11705,7 +11698,7 @@
     </row>
     <row r="713" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A713" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B713" s="6"/>
       <c r="C713" s="5"/>
@@ -11716,7 +11709,7 @@
     </row>
     <row r="714" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A714" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B714" s="6"/>
       <c r="C714" s="5"/>
@@ -11727,7 +11720,7 @@
     </row>
     <row r="715" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A715" s="8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B715" s="6"/>
       <c r="C715" s="5"/>
@@ -11738,7 +11731,7 @@
     </row>
     <row r="716" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A716" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B716" s="6"/>
       <c r="C716" s="5"/>
@@ -11749,7 +11742,7 @@
     </row>
     <row r="717" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A717" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B717" s="6"/>
       <c r="C717" s="5"/>
@@ -11760,7 +11753,7 @@
     </row>
     <row r="718" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A718" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B718" s="6"/>
       <c r="C718" s="5"/>
@@ -11771,7 +11764,7 @@
     </row>
     <row r="719" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A719" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B719" s="6"/>
       <c r="C719" s="5"/>
@@ -11782,7 +11775,7 @@
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A720" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B720" s="6"/>
       <c r="C720" s="5"/>
@@ -11793,7 +11786,7 @@
     </row>
     <row r="721" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A721" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B721" s="6"/>
       <c r="C721" s="5"/>
@@ -11804,7 +11797,7 @@
     </row>
     <row r="722" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A722" s="8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B722" s="6"/>
       <c r="C722" s="5"/>
@@ -11815,7 +11808,7 @@
     </row>
     <row r="723" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A723" s="8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B723" s="6"/>
       <c r="C723" s="5"/>
@@ -11826,7 +11819,7 @@
     </row>
     <row r="724" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A724" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B724" s="6"/>
       <c r="C724" s="5"/>
@@ -11837,7 +11830,7 @@
     </row>
     <row r="725" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A725" s="8" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B725" s="6"/>
       <c r="C725" s="5"/>
@@ -11848,7 +11841,7 @@
     </row>
     <row r="726" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A726" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B726" s="6"/>
       <c r="C726" s="5"/>
@@ -11859,7 +11852,7 @@
     </row>
     <row r="727" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A727" s="8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B727" s="6"/>
       <c r="C727" s="5"/>
@@ -11870,7 +11863,7 @@
     </row>
     <row r="728" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A728" s="8" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B728" s="6"/>
       <c r="C728" s="5"/>
@@ -11881,7 +11874,7 @@
     </row>
     <row r="729" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A729" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B729" s="6"/>
       <c r="C729" s="5"/>
@@ -11892,7 +11885,7 @@
     </row>
     <row r="730" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A730" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B730" s="6"/>
       <c r="C730" s="5"/>
@@ -11903,7 +11896,7 @@
     </row>
     <row r="731" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A731" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B731" s="6"/>
       <c r="C731" s="5"/>
@@ -11914,7 +11907,7 @@
     </row>
     <row r="732" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A732" s="8" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B732" s="6"/>
       <c r="C732" s="5"/>
@@ -11925,7 +11918,7 @@
     </row>
     <row r="733" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A733" s="8" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B733" s="6"/>
       <c r="C733" s="5"/>
@@ -11936,7 +11929,7 @@
     </row>
     <row r="734" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A734" s="8" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B734" s="6"/>
       <c r="C734" s="5"/>
@@ -11947,7 +11940,7 @@
     </row>
     <row r="735" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A735" s="8" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B735" s="6"/>
       <c r="C735" s="5"/>
@@ -11958,7 +11951,7 @@
     </row>
     <row r="736" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A736" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B736" s="6"/>
       <c r="C736" s="5"/>
@@ -11969,7 +11962,7 @@
     </row>
     <row r="737" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A737" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B737" s="6"/>
       <c r="C737" s="5"/>
@@ -11980,7 +11973,7 @@
     </row>
     <row r="738" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A738" s="8" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B738" s="6"/>
       <c r="C738" s="5"/>
@@ -11991,7 +11984,7 @@
     </row>
     <row r="739" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A739" s="8" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B739" s="6"/>
       <c r="C739" s="5"/>
@@ -12002,7 +11995,7 @@
     </row>
     <row r="740" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A740" s="8" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B740" s="6"/>
       <c r="C740" s="5"/>
@@ -12013,7 +12006,7 @@
     </row>
     <row r="741" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A741" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B741" s="6"/>
       <c r="C741" s="5"/>
@@ -12024,7 +12017,7 @@
     </row>
     <row r="742" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A742" s="8" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B742" s="6"/>
       <c r="C742" s="5"/>
@@ -12035,7 +12028,7 @@
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A743" s="8" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B743" s="6"/>
       <c r="C743" s="5"/>
@@ -12046,7 +12039,7 @@
     </row>
     <row r="744" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A744" s="8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B744" s="6"/>
       <c r="C744" s="5"/>
@@ -12057,7 +12050,7 @@
     </row>
     <row r="745" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A745" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B745" s="6"/>
       <c r="C745" s="5"/>
@@ -12068,7 +12061,7 @@
     </row>
     <row r="746" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A746" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B746" s="6"/>
       <c r="C746" s="5"/>
@@ -12157,10 +12150,10 @@
         <v>172</v>
       </c>
       <c r="F750" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G750" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.35">
@@ -12180,10 +12173,10 @@
         <v>173</v>
       </c>
       <c r="F751" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G751" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="752" spans="1:7" x14ac:dyDescent="0.35">
@@ -12281,7 +12274,7 @@
         <v>135</v>
       </c>
       <c r="F756" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G756" s="5"/>
     </row>
@@ -12302,7 +12295,7 @@
         <v>136</v>
       </c>
       <c r="F757" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G757" s="5"/>
     </row>
@@ -12323,7 +12316,7 @@
         <v>175</v>
       </c>
       <c r="F758" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G758" s="5"/>
     </row>
@@ -12344,7 +12337,7 @@
         <v>176</v>
       </c>
       <c r="F759" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G759" s="5"/>
     </row>
@@ -12421,10 +12414,10 @@
       <c r="D764" s="5"/>
       <c r="E764" s="5"/>
       <c r="F764" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G764" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="765" spans="1:7" x14ac:dyDescent="0.35">
@@ -12469,10 +12462,10 @@
       <c r="D768" s="5"/>
       <c r="E768" s="5"/>
       <c r="F768" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G768" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="769" spans="1:7" x14ac:dyDescent="0.35">
@@ -12484,10 +12477,10 @@
       <c r="D769" s="5"/>
       <c r="E769" s="5"/>
       <c r="F769" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G769" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.35">
@@ -12567,7 +12560,7 @@
       <c r="E775" s="5"/>
       <c r="F775" s="5"/>
       <c r="G775" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="776" spans="1:7" x14ac:dyDescent="0.35">
@@ -12754,33 +12747,33 @@
       <c r="A792" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B792" s="6"/>
-      <c r="C792" s="5"/>
-      <c r="D792" s="5"/>
-      <c r="E792" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F792" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G792" s="5" t="s">
-        <v>177</v>
+      <c r="B792" s="6">
+        <v>100000</v>
+      </c>
+      <c r="C792" s="5">
+        <v>100000</v>
+      </c>
+      <c r="D792" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E792" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F792" s="5">
+        <v>50000</v>
+      </c>
+      <c r="G792" s="5">
+        <v>75000</v>
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A793" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B793" s="6">
-        <v>100000</v>
-      </c>
-      <c r="C793" s="5">
-        <v>100000</v>
-      </c>
-      <c r="D793" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E793" s="5"/>
+      <c r="B793" s="6"/>
+      <c r="C793" s="6"/>
+      <c r="D793" s="6"/>
+      <c r="E793" s="6"/>
       <c r="F793" s="5"/>
       <c r="G793" s="5"/>
     </row>
